--- a/ENVIAR_ADRIAN.xlsx
+++ b/ENVIAR_ADRIAN.xlsx
@@ -1,26 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Allan\Desktop\SITE_CÓDIGOS_BRASIL\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E7A90E1-49CE-41BF-880F-3843914726AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -177,8 +166,9 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -187,12 +177,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -204,12 +199,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFbdd7ee"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -217,32 +211,85 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFc6c6c6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFc6c6c6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFc6c6c6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFc6c6c6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+  <cellXfs count="15">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -253,10 +300,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -283,82 +330,82 @@
         <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -370,403 +417,920 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:tint val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="9500"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot rev="0" lon="0" lat="0"/>
+            </a:camera>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:tint val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:N39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:N39"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="37.88671875" customWidth="1"/>
-    <col min="6" max="6" width="59.109375" customWidth="1"/>
+    <col min="1" max="1" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="12" width="37.86214285714286" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="12" width="59.14785714285715" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B2">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1"/>
+      <c r="B2" s="4">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="J2" t="s">
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="D3" t="s">
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="D4" t="s">
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="98.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J4" t="s">
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="D5" t="s">
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="D6" t="s">
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="58.5">
+      <c r="A6" s="1"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J6" t="s">
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="D7" t="s">
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="1"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="2:14" ht="73.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D8" s="1"/>
-      <c r="E8" s="2" t="s">
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="45.75">
+      <c r="A8" s="1"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="2:14" ht="73.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D9" s="1" t="s">
+      <c r="F8" s="6"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="1"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="2:14" ht="73.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D10" t="s">
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="1"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="2:14" ht="73.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D11" t="s">
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="1"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="12" spans="2:14" ht="73.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E12" s="2" t="s">
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="36" customFormat="1" s="7">
+      <c r="A12" s="3"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="2"/>
-      <c r="H12" s="2" t="s">
+      <c r="F12" s="6"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-    </row>
-    <row r="13" spans="2:14" ht="73.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-    </row>
-    <row r="14" spans="2:14" ht="73.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E14" t="s">
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="73.8" customFormat="1" s="7">
+      <c r="A13" s="3"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="73.8">
+      <c r="A14" s="1"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="15" spans="2:14" ht="73.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E15" t="s">
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="73.8">
+      <c r="A15" s="1"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="16" spans="2:14" ht="73.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D16" t="s">
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="73.8">
+      <c r="A16" s="1"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="17" spans="2:6" ht="73.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D17" t="s">
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="73.8">
+      <c r="A17" s="1"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="18" spans="2:6" ht="73.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D18" t="s">
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="73.8">
+      <c r="A18" s="1"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="19" spans="2:6" ht="73.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E19" t="s">
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="73.8">
+      <c r="A19" s="1"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="20" spans="2:6" ht="73.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E20" t="s">
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="73.8">
+      <c r="A20" s="1"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="21" spans="2:6" ht="73.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D21" t="s">
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="73.8">
+      <c r="A21" s="1"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B22" s="3" t="s">
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+      <c r="A22" s="1"/>
+      <c r="B22" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C23" s="4" t="s">
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+      <c r="A23" s="1"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4" t="s">
+      <c r="D23" s="11"/>
+      <c r="E23" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="4"/>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E24" t="s">
+      <c r="F23" s="11"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+      <c r="A24" s="1"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E25" t="s">
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+      <c r="A25" s="1"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C27" t="s">
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+      <c r="A26" s="1"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+      <c r="A27" s="1"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E28" t="s">
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+      <c r="A28" s="1"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C30" t="s">
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+      <c r="A29" s="1"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+      <c r="A30" s="1"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E31" t="s">
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+      <c r="A31" s="1"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="E32" t="s">
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+      <c r="A32" s="1"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="E33" t="s">
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+      <c r="A33" s="1"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="35" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C35" t="s">
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+      <c r="A34" s="1"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+      <c r="A35" s="1"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="36" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C36" t="s">
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+      <c r="A36" s="1"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="38" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C38" t="s">
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+      <c r="A37" s="1"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+      <c r="A38" s="1"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="39" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="D39" t="s">
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+      <c r="A39" s="1"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="3">
